--- a/bom/bom.xlsx
+++ b/bom/bom.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luka\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54E3D7B1-B2F6-451C-A573-FEDABEEC56CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA5ECEAE-1842-407A-A2FC-D51ED29E05A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{686FA2F2-D2B9-4BB6-B2A8-6DB22F06632F}"/>
   </bookViews>
@@ -389,9 +389,6 @@
     <t>R2 &amp; R3</t>
   </si>
   <si>
-    <t>RP</t>
-  </si>
-  <si>
     <t>R1</t>
   </si>
   <si>
@@ -404,10 +401,13 @@
     <t>C3</t>
   </si>
   <si>
-    <t>C8 x 2?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C4, </t>
+    <t>C8</t>
+  </si>
+  <si>
+    <t>C4 + Cn</t>
+  </si>
+  <si>
+    <t>R12, R13, R17, RP</t>
   </si>
 </sst>
 </file>
@@ -1133,7 +1133,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>77</v>
@@ -1155,7 +1155,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>36</v>
@@ -1171,7 +1171,7 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>23</v>
@@ -1182,7 +1182,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>56</v>
@@ -1193,7 +1193,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>72</v>
@@ -1204,7 +1204,7 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>24</v>
@@ -1215,7 +1215,7 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>25</v>
